--- a/output/pdf_financials_xlsx/ONE.xlsx
+++ b/output/pdf_financials_xlsx/ONE.xlsx
@@ -1053,31 +1053,31 @@
         <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>4.1e-05</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.00121</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.00303</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.000966</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.004482</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.015343</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.004027</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.01814</v>
       </c>
     </row>
     <row r="13">
@@ -2059,31 +2059,31 @@
         <v>-0.943927</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.024908</v>
+        <v>-0.024949</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.387624</v>
+        <v>-0.388834</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.313757</v>
+        <v>-0.323657</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.657168</v>
+        <v>-0.660198</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.656847</v>
+        <v>-0.657813</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.662004</v>
+        <v>-0.666486</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.722112</v>
+        <v>-0.737455</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-0.31879</v>
+        <v>-0.322817</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-1.126086</v>
+        <v>-1.144226</v>
       </c>
     </row>
     <row r="28">
@@ -2175,31 +2175,31 @@
         <v>-0.943927</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.024908</v>
+        <v>-0.024949</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.387624</v>
+        <v>-0.388834</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.313757</v>
+        <v>-0.323657</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.657168</v>
+        <v>-0.660198</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.656847</v>
+        <v>-0.657813</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.662004</v>
+        <v>-0.666486</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.722112</v>
+        <v>-0.737455</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-0.31879</v>
+        <v>-0.322817</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-1.126086</v>
+        <v>-1.144226</v>
       </c>
     </row>
     <row r="30">
@@ -2233,31 +2233,31 @@
         <v>-1444.174660730405</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-4.942190969211508</v>
+        <v>-4.950326099681143</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-190.9788290707357</v>
+        <v>-191.5749850960994</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-110.8262953582921</v>
+        <v>-114.3232064201874</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-125.9446789998294</v>
+        <v>-126.5253712693396</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-74.1910780543178</v>
+        <v>-74.3001880622808</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-64.47190814269436</v>
+        <v>-64.90840564466649</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-152.186658967188</v>
+        <v>-155.4202292561924</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>-77.19858190377481</v>
+        <v>-78.17376521983398</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>-146.6271176950832</v>
+        <v>-148.989118390402</v>
       </c>
     </row>
     <row r="31">
@@ -2423,22 +2423,22 @@
         <v>0.283712</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.962337</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.994924</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.487179</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.27254</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.139126</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.159133</v>
       </c>
     </row>
     <row r="35">
@@ -2539,22 +2539,22 @@
         <v>0.283712</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.962337</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.994924</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.487179</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.27254</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.139126</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.159133</v>
       </c>
     </row>
     <row r="37">
@@ -3235,22 +3235,22 @@
         <v>0.311124</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>1.04768</v>
+        <v>0.085343</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>1.026667</v>
+        <v>0.031743</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.70131</v>
+        <v>0.214131</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.3586</v>
+        <v>0.08606</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.145163</v>
+        <v>0.006037</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>3.099191</v>
+        <v>2.940058</v>
       </c>
     </row>
     <row r="49">
@@ -8573,7 +8573,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -25009,7 +25009,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -25108,7 +25108,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -25907,7 +25907,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -26004,7 +26004,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -28649,7 +28649,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">

--- a/output/pdf_financials_xlsx/ONE.xlsx
+++ b/output/pdf_financials_xlsx/ONE.xlsx
@@ -2099,49 +2099,49 @@
         <v>0.012503</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>0.012849</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>0.00873</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>0.007411</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>0.007488</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>0.006112</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>0.005287</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>0.00242</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>0.001346</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0</v>
+        <v>0.005376</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0</v>
+        <v>0.00584</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0</v>
+        <v>0.007214</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0</v>
+        <v>0.006556</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0</v>
+        <v>0.009848000000000001</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>0</v>
+        <v>0.008794</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>0</v>
+        <v>0.006729</v>
       </c>
     </row>
     <row r="29">
@@ -2157,49 +2157,49 @@
         <v>-1.587662</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-3.646307</v>
+        <v>-3.633458</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-2.524339</v>
+        <v>-2.515609</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-3.17208</v>
+        <v>-3.164669</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-2.073332</v>
+        <v>-2.065844</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.571724</v>
+        <v>-1.565612</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.943927</v>
+        <v>-0.93864</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.024949</v>
+        <v>-0.022529</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.388834</v>
+        <v>-0.387488</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.323657</v>
+        <v>-0.318281</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.660198</v>
+        <v>-0.654358</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.657813</v>
+        <v>-0.650599</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.666486</v>
+        <v>-0.65993</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.737455</v>
+        <v>-0.727607</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-0.322817</v>
+        <v>-0.314023</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-1.144226</v>
+        <v>-1.137497</v>
       </c>
     </row>
     <row r="30">
@@ -2215,49 +2215,49 @@
         <v>-367.7314155346327</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-765.4808939795357</v>
+        <v>-762.7834623022954</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-270.4125487137847</v>
+        <v>-269.477372594305</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-252.1307772220054</v>
+        <v>-251.5417185633359</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-777.4285596439324</v>
+        <v>-774.6208158505536</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-1806.890843248836</v>
+        <v>-1799.8643444272</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-1444.174660730405</v>
+        <v>-1436.085739202276</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-4.950326099681143</v>
+        <v>-4.470154984156338</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-191.5749850960994</v>
+        <v>-190.9118231042485</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-114.3232064201874</v>
+        <v>-112.4242777465764</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-126.5253712693396</v>
+        <v>-125.4061492053332</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-74.3001880622808</v>
+        <v>-73.4853644624412</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-64.90840564466649</v>
+        <v>-64.2699233548563</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-155.4202292561924</v>
+        <v>-153.3447420499019</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>-78.17376521983398</v>
+        <v>-76.04419926964169</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>-148.989118390402</v>
+        <v>-148.1129385293876</v>
       </c>
     </row>
     <row r="31">
@@ -6293,49 +6293,49 @@
         <v>0</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.012849</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.00873</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.007411</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.007488</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>0.006112</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.005287</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.00242</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.001346</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.005376</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.00584</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>0.007214</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>0.006556</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>0.009848000000000001</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>0.008794</v>
       </c>
       <c r="R100" s="3" t="n">
-        <v>0</v>
+        <v>0.006729</v>
       </c>
     </row>
     <row r="101">
@@ -14602,7 +14602,11 @@
           <t>Depreciation of property and equipment (note 5)</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
@@ -18821,7 +18825,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ONE.xlsx
+++ b/output/pdf_financials_xlsx/ONE.xlsx
@@ -6635,55 +6635,55 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0</v>
+        <v>0.198126</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0</v>
+        <v>-0.186177</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0</v>
+        <v>0.445363</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0</v>
+        <v>-0.646188</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0</v>
+        <v>0.687957</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0</v>
+        <v>-0.223666</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0</v>
+        <v>-0.157073</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0</v>
+        <v>0.068595</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>0</v>
+        <v>-0.024687</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>0</v>
+        <v>0.0492</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>0</v>
+        <v>-0.481346</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>0</v>
+        <v>-0.112217</v>
       </c>
       <c r="N106" s="3" t="n">
-        <v>0</v>
+        <v>0.021133</v>
       </c>
       <c r="O106" s="3" t="n">
-        <v>0</v>
+        <v>-0.053736</v>
       </c>
       <c r="P106" s="3" t="n">
-        <v>0</v>
+        <v>0.158102</v>
       </c>
       <c r="Q106" s="3" t="n">
-        <v>0</v>
+        <v>-0.01692</v>
       </c>
       <c r="R106" s="3" t="n">
-        <v>0</v>
+        <v>0.092792</v>
       </c>
     </row>
     <row r="107">
@@ -14869,7 +14869,11 @@
           <t>Change in non-cash operating working capital (note 10)</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>
@@ -19201,7 +19205,11 @@
           <t>Change in non-cash operating working capital (note 11)</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
           <t>-</t>
@@ -21661,7 +21669,11 @@
           <t>Change in non-cash operating working capital (note 8)</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
           <t>-</t>
@@ -22534,7 +22546,11 @@
           <t>Change in non-cash operating working capital (note 7)</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
           <t>-</t>
@@ -23445,7 +23461,11 @@
           <t>Change in non-cash operating working capital (note 7)</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E156" s="5" t="n">
         <v>0.198126</v>
       </c>
